--- a/data/POISSON_DUAS_MATRIZES.xlsx
+++ b/data/POISSON_DUAS_MATRIZES.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>COEF_OVER1FT</t>
+          <t>COEF_OVER1,5FT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -1012,6 +1012,9 @@
       <c r="P2" t="n">
         <v>0.79</v>
       </c>
+      <c r="Q2" t="n">
+        <v>5.06</v>
+      </c>
       <c r="R2" t="n">
         <v>22</v>
       </c>
@@ -1112,7 +1115,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Omonia Nicosia favorito | Gols do Favorito</t>
+          <t>Omonia Nicosia favorito | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1308,6 +1311,9 @@
       <c r="P3" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="R3" t="n">
         <v>3.89</v>
       </c>
@@ -1408,7 +1414,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>MP favorito</t>
+          <t>MP favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1604,6 +1610,9 @@
       <c r="P4" t="n">
         <v>-0.12</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="R4" t="n">
         <v>3.04</v>
       </c>
@@ -1704,7 +1713,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris favorito | BTTS / Jogo Aberto</t>
+          <t>Kauno Žalgiris favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -1900,6 +1909,9 @@
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
@@ -2000,7 +2012,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -2196,6 +2208,9 @@
       <c r="P6" t="n">
         <v>-0.03</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="R6" t="n">
         <v>3.43</v>
       </c>
@@ -2296,7 +2311,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan favorito</t>
+          <t>Hapoel Ramat Gan favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -2492,6 +2507,9 @@
       <c r="P7" t="n">
         <v>0.15</v>
       </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
@@ -2592,7 +2610,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Domínio do FC Kobenhavn | Gols do Favorito</t>
+          <t>Domínio do FC Kobenhavn | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -2788,6 +2806,9 @@
       <c r="P8" t="n">
         <v>0.08</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="R8" t="n">
         <v>1.93</v>
       </c>
@@ -2888,7 +2909,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Domínio do Lech Poznań</t>
+          <t>Domínio do Lech Poznań | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -3084,6 +3105,9 @@
       <c r="P9" t="n">
         <v>-0.6</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R9" t="n">
         <v>18.67</v>
       </c>
@@ -3184,7 +3208,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -3380,6 +3404,9 @@
       <c r="P10" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q10" t="n">
+        <v>2.09</v>
+      </c>
       <c r="R10" t="n">
         <v>3.82</v>
       </c>
@@ -3480,7 +3507,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Universitatea Craiova favorito</t>
+          <t>Universitatea Craiova favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -3676,6 +3703,9 @@
       <c r="P11" t="n">
         <v>-0.08</v>
       </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
       <c r="R11" t="n">
         <v>2.56</v>
       </c>
@@ -3776,7 +3806,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -3972,6 +4002,9 @@
       <c r="P12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
       <c r="R12" t="n">
         <v>2.35</v>
       </c>
@@ -4268,6 +4301,9 @@
       <c r="P13" t="n">
         <v>0.29</v>
       </c>
+      <c r="Q13" t="n">
+        <v>4.17</v>
+      </c>
       <c r="R13" t="n">
         <v>2.39</v>
       </c>
@@ -4352,6 +4388,9 @@
       <c r="P14" t="n">
         <v>-0.16</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
       <c r="R14" t="n">
         <v>2.78</v>
       </c>
@@ -4645,6 +4684,9 @@
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
@@ -4729,6 +4771,9 @@
       <c r="P16" t="n">
         <v>-0.46</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
       <c r="R16" t="n">
         <v>4.96</v>
       </c>
@@ -4829,7 +4874,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Defensa y Justicia favorito | BTTS / Jogo Aberto</t>
+          <t>Defensa y Justicia favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY16" t="n">
@@ -5025,6 +5070,9 @@
       <c r="P17" t="n">
         <v>-0.31</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
       <c r="R17" t="n">
         <v>3.94</v>
       </c>
@@ -5125,7 +5173,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY17" t="n">
@@ -5321,6 +5369,9 @@
       <c r="P18" t="n">
         <v>0.19</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
       <c r="S18" t="n">
         <v>8.56</v>
       </c>
@@ -5396,6 +5447,9 @@
       <c r="N19" t="n">
         <v>1.8</v>
       </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
       <c r="S19" t="n">
         <v>3.04</v>
       </c>
@@ -5480,6 +5534,9 @@
       <c r="P20" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
       <c r="R20" t="n">
         <v>8.25</v>
       </c>
@@ -5580,7 +5637,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY20" t="n">
@@ -5776,6 +5833,9 @@
       <c r="P21" t="n">
         <v>-0.45</v>
       </c>
+      <c r="Q21" t="n">
+        <v>1.21</v>
+      </c>
       <c r="R21" t="n">
         <v>3.97</v>
       </c>
@@ -5876,7 +5936,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY21" t="n">
@@ -6072,6 +6132,9 @@
       <c r="P22" t="n">
         <v>-0.19</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
       <c r="S22" t="n">
         <v>13.92</v>
       </c>
@@ -6156,6 +6219,9 @@
       <c r="P23" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
       <c r="R23" t="n">
         <v>3.87</v>
       </c>
@@ -6256,7 +6322,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY23" t="n">
@@ -6452,6 +6518,9 @@
       <c r="P24" t="n">
         <v>-0.27</v>
       </c>
+      <c r="Q24" t="n">
+        <v>1.64</v>
+      </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
@@ -6552,7 +6621,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY24" t="n">
@@ -6748,6 +6817,9 @@
       <c r="P25" t="n">
         <v>-0.37</v>
       </c>
+      <c r="Q25" t="n">
+        <v>1.34</v>
+      </c>
       <c r="R25" t="n">
         <v>4.12</v>
       </c>
@@ -6848,7 +6920,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY25" t="n">
@@ -7044,6 +7116,9 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.19</v>
+      </c>
       <c r="R26" t="n">
         <v>13.25</v>
       </c>
@@ -7144,7 +7219,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY26" t="n">
@@ -7340,6 +7415,9 @@
       <c r="P27" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="Q27" t="n">
+        <v>3.94</v>
+      </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
@@ -7440,7 +7518,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Domínio do Independiente del Valle | Gols do Favorito</t>
+          <t>Domínio do Independiente del Valle | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY27" t="n">
@@ -7636,6 +7714,9 @@
       <c r="P28" t="n">
         <v>-0.32</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
       <c r="R28" t="n">
         <v>2.08</v>
       </c>
@@ -7736,7 +7817,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY28" t="n">
@@ -7932,6 +8013,9 @@
       <c r="P29" t="n">
         <v>-0.18</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1.71</v>
+      </c>
       <c r="R29" t="n">
         <v>2.52</v>
       </c>
@@ -8228,6 +8312,9 @@
       <c r="P30" t="n">
         <v>-0.53</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1.06</v>
+      </c>
       <c r="R30" t="n">
         <v>4.36</v>
       </c>
@@ -8328,7 +8415,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY30" t="n">
@@ -8524,6 +8611,9 @@
       <c r="P31" t="n">
         <v>-0.15</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
       <c r="R31" t="n">
         <v>6.04</v>
       </c>
@@ -8808,6 +8898,9 @@
       <c r="P32" t="n">
         <v>-0.04</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="n">
         <v>5.61</v>
       </c>
@@ -8908,7 +9001,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bragantino favorito</t>
+          <t>Bragantino favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY32" t="n">
@@ -9104,6 +9197,9 @@
       <c r="P33" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
       <c r="R33" t="n">
         <v>6.25</v>
       </c>
@@ -9204,7 +9300,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY33" t="n">
@@ -9397,6 +9493,9 @@
       <c r="P34" t="n">
         <v>0.22</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.53</v>
+      </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
@@ -9764,6 +9863,9 @@
       </c>
       <c r="N36" t="n">
         <v>1.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>2.9</v>
@@ -9903,7 +10005,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>COEF_OVER1FT</t>
+          <t>COEF_OVER1,5FT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -10360,6 +10462,9 @@
       <c r="P2" t="n">
         <v>0.79</v>
       </c>
+      <c r="Q2" t="n">
+        <v>5.06</v>
+      </c>
       <c r="R2" t="n">
         <v>22</v>
       </c>
@@ -10460,7 +10565,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Omonia Nicosia favorito | Gols do Favorito</t>
+          <t>Omonia Nicosia favorito | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -10656,6 +10761,9 @@
       <c r="P3" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="R3" t="n">
         <v>3.89</v>
       </c>
@@ -10756,7 +10864,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>MP favorito</t>
+          <t>MP favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -10952,6 +11060,9 @@
       <c r="P4" t="n">
         <v>-0.12</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="R4" t="n">
         <v>3.04</v>
       </c>
@@ -11052,7 +11163,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris favorito | BTTS / Jogo Aberto</t>
+          <t>Kauno Žalgiris favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -11248,6 +11359,9 @@
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
@@ -11348,7 +11462,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -11544,6 +11658,9 @@
       <c r="P6" t="n">
         <v>-0.03</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="R6" t="n">
         <v>3.43</v>
       </c>
@@ -11644,7 +11761,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan favorito</t>
+          <t>Hapoel Ramat Gan favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -11840,6 +11957,9 @@
       <c r="P7" t="n">
         <v>0.15</v>
       </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
@@ -11940,7 +12060,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>FC Kobenhavn favorito | Gols do Favorito</t>
+          <t>FC Kobenhavn favorito | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -12136,6 +12256,9 @@
       <c r="P8" t="n">
         <v>0.08</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="R8" t="n">
         <v>1.93</v>
       </c>
@@ -12236,7 +12359,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lech Poznań favorito</t>
+          <t>Lech Poznań favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -12432,6 +12555,9 @@
       <c r="P9" t="n">
         <v>-0.6</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R9" t="n">
         <v>18.67</v>
       </c>
@@ -12532,7 +12658,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -12728,6 +12854,9 @@
       <c r="P10" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q10" t="n">
+        <v>2.09</v>
+      </c>
       <c r="R10" t="n">
         <v>3.82</v>
       </c>
@@ -12828,7 +12957,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Universitatea Craiova favorito</t>
+          <t>Universitatea Craiova favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -13024,6 +13153,9 @@
       <c r="P11" t="n">
         <v>-0.08</v>
       </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
       <c r="R11" t="n">
         <v>2.56</v>
       </c>
@@ -13124,7 +13256,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -13320,6 +13452,9 @@
       <c r="P12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
       <c r="R12" t="n">
         <v>2.35</v>
       </c>
@@ -13616,6 +13751,9 @@
       <c r="P13" t="n">
         <v>0.29</v>
       </c>
+      <c r="Q13" t="n">
+        <v>4.17</v>
+      </c>
       <c r="R13" t="n">
         <v>2.39</v>
       </c>
@@ -13700,6 +13838,9 @@
       <c r="P14" t="n">
         <v>-0.16</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
       <c r="R14" t="n">
         <v>2.78</v>
       </c>
@@ -13993,6 +14134,9 @@
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
@@ -14077,6 +14221,9 @@
       <c r="P16" t="n">
         <v>-0.46</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
       <c r="R16" t="n">
         <v>4.96</v>
       </c>
@@ -14177,7 +14324,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY16" t="n">
@@ -14373,6 +14520,9 @@
       <c r="P17" t="n">
         <v>-0.31</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
       <c r="R17" t="n">
         <v>3.94</v>
       </c>
@@ -14473,7 +14623,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nacional Asunción favorito | BTTS / Jogo Aberto</t>
+          <t>Nacional Asunción favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY17" t="n">
@@ -14669,6 +14819,9 @@
       <c r="P18" t="n">
         <v>0.19</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
       <c r="S18" t="n">
         <v>8.56</v>
       </c>
@@ -14744,6 +14897,9 @@
       <c r="N19" t="n">
         <v>1.8</v>
       </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
       <c r="S19" t="n">
         <v>3.04</v>
       </c>
@@ -14828,6 +14984,9 @@
       <c r="P20" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
       <c r="R20" t="n">
         <v>8.25</v>
       </c>
@@ -14928,7 +15087,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vasco da Gama favorito | BTTS / Jogo Aberto</t>
+          <t>Vasco da Gama favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY20" t="n">
@@ -15124,6 +15283,9 @@
       <c r="P21" t="n">
         <v>-0.45</v>
       </c>
+      <c r="Q21" t="n">
+        <v>1.21</v>
+      </c>
       <c r="R21" t="n">
         <v>3.97</v>
       </c>
@@ -15224,7 +15386,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>River Plate favorito | BTTS / Jogo Aberto</t>
+          <t>River Plate favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY21" t="n">
@@ -15420,6 +15582,9 @@
       <c r="P22" t="n">
         <v>-0.19</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
       <c r="S22" t="n">
         <v>13.92</v>
       </c>
@@ -15504,6 +15669,9 @@
       <c r="P23" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
       <c r="R23" t="n">
         <v>3.87</v>
       </c>
@@ -15604,7 +15772,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mirassol favorito | BTTS / Jogo Aberto</t>
+          <t>Mirassol favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY23" t="n">
@@ -15800,6 +15968,9 @@
       <c r="P24" t="n">
         <v>-0.27</v>
       </c>
+      <c r="Q24" t="n">
+        <v>1.64</v>
+      </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
@@ -15900,7 +16071,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY24" t="n">
@@ -16096,6 +16267,9 @@
       <c r="P25" t="n">
         <v>-0.37</v>
       </c>
+      <c r="Q25" t="n">
+        <v>1.34</v>
+      </c>
       <c r="R25" t="n">
         <v>4.12</v>
       </c>
@@ -16196,7 +16370,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY25" t="n">
@@ -16392,6 +16566,9 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.19</v>
+      </c>
       <c r="R26" t="n">
         <v>13.25</v>
       </c>
@@ -16492,7 +16669,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY26" t="n">
@@ -16688,6 +16865,9 @@
       <c r="P27" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="Q27" t="n">
+        <v>3.94</v>
+      </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
@@ -16788,7 +16968,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Domínio do Independiente del Valle | Gols do Favorito</t>
+          <t>Domínio do Independiente del Valle | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY27" t="n">
@@ -16984,6 +17164,9 @@
       <c r="P28" t="n">
         <v>-0.32</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
       <c r="R28" t="n">
         <v>2.08</v>
       </c>
@@ -17084,7 +17267,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY28" t="n">
@@ -17280,6 +17463,9 @@
       <c r="P29" t="n">
         <v>-0.18</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1.71</v>
+      </c>
       <c r="R29" t="n">
         <v>2.52</v>
       </c>
@@ -17576,6 +17762,9 @@
       <c r="P30" t="n">
         <v>-0.53</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1.06</v>
+      </c>
       <c r="R30" t="n">
         <v>4.36</v>
       </c>
@@ -17676,7 +17865,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Instituto favorito | BTTS / Jogo Aberto</t>
+          <t>Instituto favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY30" t="n">
@@ -17872,6 +18061,9 @@
       <c r="P31" t="n">
         <v>-0.15</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
       <c r="R31" t="n">
         <v>6.04</v>
       </c>
@@ -18162,6 +18354,9 @@
       <c r="P32" t="n">
         <v>-0.04</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="n">
         <v>5.61</v>
       </c>
@@ -18262,7 +18457,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Domínio do Bragantino</t>
+          <t>Domínio do Bragantino | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY32" t="n">
@@ -18458,6 +18653,9 @@
       <c r="P33" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
       <c r="R33" t="n">
         <v>6.25</v>
       </c>
@@ -18558,7 +18756,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Firpo favorito | BTTS / Jogo Aberto</t>
+          <t>Firpo favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY33" t="n">
@@ -18751,6 +18949,9 @@
       <c r="P34" t="n">
         <v>0.22</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.53</v>
+      </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
@@ -19118,6 +19319,9 @@
       </c>
       <c r="N36" t="n">
         <v>1.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>2.9</v>
@@ -19257,7 +19461,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>COEF_OVER1FT</t>
+          <t>COEF_OVER1,5FT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -19714,6 +19918,9 @@
       <c r="P2" t="n">
         <v>0.79</v>
       </c>
+      <c r="Q2" t="n">
+        <v>5.06</v>
+      </c>
       <c r="R2" t="n">
         <v>22</v>
       </c>
@@ -19814,7 +20021,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | Gols do Favorito</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -20010,6 +20217,9 @@
       <c r="P3" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="R3" t="n">
         <v>3.89</v>
       </c>
@@ -20110,7 +20320,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>MP favorito</t>
+          <t>MP favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -20306,6 +20516,9 @@
       <c r="P4" t="n">
         <v>-0.12</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="R4" t="n">
         <v>3.04</v>
       </c>
@@ -20406,7 +20619,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Domínio do Kauno Žalgiris | BTTS / Jogo Aberto</t>
+          <t>Domínio do Kauno Žalgiris | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -20602,6 +20815,9 @@
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
@@ -20702,7 +20918,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Domínio do Maccabi Netanya</t>
+          <t>Domínio do Maccabi Netanya | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY5" t="n">
@@ -20898,6 +21114,9 @@
       <c r="P6" t="n">
         <v>-0.03</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="R6" t="n">
         <v>3.43</v>
       </c>
@@ -20998,7 +21217,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -21194,6 +21413,9 @@
       <c r="P7" t="n">
         <v>0.15</v>
       </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
@@ -21294,7 +21516,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Domínio do FC Kobenhavn | Gols do Favorito</t>
+          <t>Domínio do FC Kobenhavn | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -21490,6 +21712,9 @@
       <c r="P8" t="n">
         <v>0.08</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="R8" t="n">
         <v>1.93</v>
       </c>
@@ -21590,7 +21815,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Domínio do Lech Poznań</t>
+          <t>Domínio do Lech Poznań | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -21786,6 +22011,9 @@
       <c r="P9" t="n">
         <v>-0.6</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R9" t="n">
         <v>18.67</v>
       </c>
@@ -21886,7 +22114,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Aldosivi favorito | BTTS / Jogo Aberto</t>
+          <t>Aldosivi favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -22082,6 +22310,9 @@
       <c r="P10" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q10" t="n">
+        <v>2.09</v>
+      </c>
       <c r="R10" t="n">
         <v>3.82</v>
       </c>
@@ -22182,7 +22413,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Universitatea Craiova favorito</t>
+          <t>Universitatea Craiova favorito | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY10" t="n">
@@ -22378,6 +22609,9 @@
       <c r="P11" t="n">
         <v>-0.08</v>
       </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
       <c r="R11" t="n">
         <v>2.56</v>
       </c>
@@ -22478,7 +22712,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Domínio do Hapoel Be'er Sheva</t>
+          <t>Domínio do Hapoel Be'er Sheva | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY11" t="n">
@@ -22674,6 +22908,9 @@
       <c r="P12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
       <c r="R12" t="n">
         <v>2.35</v>
       </c>
@@ -22970,6 +23207,9 @@
       <c r="P13" t="n">
         <v>0.29</v>
       </c>
+      <c r="Q13" t="n">
+        <v>4.17</v>
+      </c>
       <c r="R13" t="n">
         <v>2.39</v>
       </c>
@@ -23054,6 +23294,9 @@
       <c r="P14" t="n">
         <v>-0.16</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
       <c r="R14" t="n">
         <v>2.78</v>
       </c>
@@ -23347,6 +23590,9 @@
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
@@ -23431,6 +23677,9 @@
       <c r="P16" t="n">
         <v>-0.46</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
       <c r="R16" t="n">
         <v>4.96</v>
       </c>
@@ -23531,7 +23780,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Defensa y Justicia favorito | BTTS / Jogo Aberto</t>
+          <t>Defensa y Justicia favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY16" t="n">
@@ -23727,6 +23976,9 @@
       <c r="P17" t="n">
         <v>-0.31</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
       <c r="R17" t="n">
         <v>3.94</v>
       </c>
@@ -23827,7 +24079,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY17" t="n">
@@ -24023,6 +24275,9 @@
       <c r="P18" t="n">
         <v>0.19</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
       <c r="S18" t="n">
         <v>8.56</v>
       </c>
@@ -24098,6 +24353,9 @@
       <c r="N19" t="n">
         <v>1.8</v>
       </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
       <c r="S19" t="n">
         <v>3.04</v>
       </c>
@@ -24182,6 +24440,9 @@
       <c r="P20" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
       <c r="R20" t="n">
         <v>8.25</v>
       </c>
@@ -24282,7 +24543,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jogo equilibrado | BTTS / Jogo Aberto</t>
+          <t>Jogo equilibrado | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY20" t="n">
@@ -24478,6 +24739,9 @@
       <c r="P21" t="n">
         <v>-0.45</v>
       </c>
+      <c r="Q21" t="n">
+        <v>1.21</v>
+      </c>
       <c r="R21" t="n">
         <v>3.97</v>
       </c>
@@ -24578,7 +24842,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>River Plate favorito | BTTS / Jogo Aberto</t>
+          <t>River Plate favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY21" t="n">
@@ -24774,6 +25038,9 @@
       <c r="P22" t="n">
         <v>-0.19</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
       <c r="S22" t="n">
         <v>13.92</v>
       </c>
@@ -24858,6 +25125,9 @@
       <c r="P23" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
       <c r="R23" t="n">
         <v>3.87</v>
       </c>
@@ -24958,7 +25228,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mirassol favorito | BTTS / Jogo Aberto</t>
+          <t>Mirassol favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY23" t="n">
@@ -25154,6 +25424,9 @@
       <c r="P24" t="n">
         <v>-0.27</v>
       </c>
+      <c r="Q24" t="n">
+        <v>1.64</v>
+      </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
@@ -25254,7 +25527,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Flamengo favorito | BTTS / Jogo Aberto</t>
+          <t>Flamengo favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY24" t="n">
@@ -25450,6 +25723,9 @@
       <c r="P25" t="n">
         <v>-0.37</v>
       </c>
+      <c r="Q25" t="n">
+        <v>1.34</v>
+      </c>
       <c r="R25" t="n">
         <v>4.12</v>
       </c>
@@ -25550,7 +25826,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds favorito | BTTS / Jogo Aberto</t>
+          <t>Pittsburgh Riverhounds favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY25" t="n">
@@ -25746,6 +26022,9 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.19</v>
+      </c>
       <c r="R26" t="n">
         <v>13.25</v>
       </c>
@@ -25846,7 +26125,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jogo equilibrado</t>
+          <t>Jogo equilibrado | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY26" t="n">
@@ -26042,6 +26321,9 @@
       <c r="P27" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="Q27" t="n">
+        <v>3.94</v>
+      </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
@@ -26142,7 +26424,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Domínio do Independiente del Valle | Gols do Favorito</t>
+          <t>Domínio do Independiente del Valle | Tendência Over 1,5FT | Gols do Favorito</t>
         </is>
       </c>
       <c r="AY27" t="n">
@@ -26338,6 +26620,9 @@
       <c r="P28" t="n">
         <v>-0.32</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
       <c r="R28" t="n">
         <v>2.08</v>
       </c>
@@ -26438,7 +26723,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Palmeiras favorito | BTTS / Jogo Aberto</t>
+          <t>Palmeiras favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY28" t="n">
@@ -26634,6 +26919,9 @@
       <c r="P29" t="n">
         <v>-0.18</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1.71</v>
+      </c>
       <c r="R29" t="n">
         <v>2.52</v>
       </c>
@@ -26930,6 +27218,9 @@
       <c r="P30" t="n">
         <v>-0.53</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1.06</v>
+      </c>
       <c r="R30" t="n">
         <v>4.36</v>
       </c>
@@ -27030,7 +27321,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Instituto favorito | BTTS / Jogo Aberto</t>
+          <t>Instituto favorito | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY30" t="n">
@@ -27226,6 +27517,9 @@
       <c r="P31" t="n">
         <v>-0.15</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
       <c r="R31" t="n">
         <v>6.04</v>
       </c>
@@ -27516,6 +27810,9 @@
       <c r="P32" t="n">
         <v>-0.04</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="n">
         <v>5.61</v>
       </c>
@@ -27616,7 +27913,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Domínio do Bragantino</t>
+          <t>Domínio do Bragantino | Tendência Over 1,5FT</t>
         </is>
       </c>
       <c r="AY32" t="n">
@@ -27812,6 +28109,9 @@
       <c r="P33" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
       <c r="R33" t="n">
         <v>6.25</v>
       </c>
@@ -27912,7 +28212,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Domínio do Firpo | BTTS / Jogo Aberto</t>
+          <t>Domínio do Firpo | Tendência Under | BTTS / Jogo Aberto</t>
         </is>
       </c>
       <c r="AY33" t="n">
@@ -28105,6 +28405,9 @@
       <c r="P34" t="n">
         <v>0.22</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.53</v>
+      </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
@@ -28472,6 +28775,9 @@
       </c>
       <c r="N36" t="n">
         <v>1.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>2.9</v>
@@ -28611,7 +28917,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>COEF_OVER1FT</t>
+          <t>COEF_OVER1,5FT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -29123,6 +29429,9 @@
       <c r="P2" t="n">
         <v>0.79</v>
       </c>
+      <c r="Q2" t="n">
+        <v>5.06</v>
+      </c>
       <c r="R2" t="n">
         <v>22</v>
       </c>
@@ -29456,6 +29765,9 @@
       <c r="P3" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="R3" t="n">
         <v>3.89</v>
       </c>
@@ -29789,6 +30101,9 @@
       <c r="P4" t="n">
         <v>-0.12</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="R4" t="n">
         <v>3.04</v>
       </c>
@@ -30122,6 +30437,9 @@
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
@@ -30455,6 +30773,9 @@
       <c r="P6" t="n">
         <v>-0.03</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="R6" t="n">
         <v>3.43</v>
       </c>
@@ -30788,6 +31109,9 @@
       <c r="P7" t="n">
         <v>0.15</v>
       </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
@@ -31121,6 +31445,9 @@
       <c r="P8" t="n">
         <v>0.08</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="R8" t="n">
         <v>1.93</v>
       </c>
@@ -31454,6 +31781,9 @@
       <c r="P9" t="n">
         <v>-0.6</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R9" t="n">
         <v>18.67</v>
       </c>
@@ -31787,6 +32117,9 @@
       <c r="P10" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q10" t="n">
+        <v>2.09</v>
+      </c>
       <c r="R10" t="n">
         <v>3.82</v>
       </c>
@@ -32120,6 +32453,9 @@
       <c r="P11" t="n">
         <v>-0.08</v>
       </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
       <c r="R11" t="n">
         <v>2.56</v>
       </c>
@@ -32453,6 +32789,9 @@
       <c r="P12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
       <c r="R12" t="n">
         <v>2.35</v>
       </c>
@@ -32786,6 +33125,9 @@
       <c r="P13" t="n">
         <v>0.29</v>
       </c>
+      <c r="Q13" t="n">
+        <v>4.17</v>
+      </c>
       <c r="R13" t="n">
         <v>2.39</v>
       </c>
@@ -33039,6 +33381,9 @@
       <c r="P14" t="n">
         <v>-0.16</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
       <c r="R14" t="n">
         <v>2.78</v>
       </c>
@@ -33369,6 +33714,9 @@
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
@@ -33622,6 +33970,9 @@
       <c r="P16" t="n">
         <v>-0.46</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
       <c r="R16" t="n">
         <v>4.96</v>
       </c>
@@ -33955,6 +34306,9 @@
       <c r="P17" t="n">
         <v>-0.31</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
       <c r="R17" t="n">
         <v>3.94</v>
       </c>
@@ -34288,6 +34642,9 @@
       <c r="P18" t="n">
         <v>0.19</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
       <c r="S18" t="n">
         <v>8.56</v>
       </c>
@@ -34532,6 +34889,9 @@
       <c r="N19" t="n">
         <v>1.8</v>
       </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
       <c r="S19" t="n">
         <v>3.04</v>
       </c>
@@ -34785,6 +35145,9 @@
       <c r="P20" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
       <c r="R20" t="n">
         <v>8.25</v>
       </c>
@@ -35118,6 +35481,9 @@
       <c r="P21" t="n">
         <v>-0.45</v>
       </c>
+      <c r="Q21" t="n">
+        <v>1.21</v>
+      </c>
       <c r="R21" t="n">
         <v>3.97</v>
       </c>
@@ -35451,6 +35817,9 @@
       <c r="P22" t="n">
         <v>-0.19</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
       <c r="S22" t="n">
         <v>13.92</v>
       </c>
@@ -35704,6 +36073,9 @@
       <c r="P23" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
       <c r="R23" t="n">
         <v>3.87</v>
       </c>
@@ -36037,6 +36409,9 @@
       <c r="P24" t="n">
         <v>-0.27</v>
       </c>
+      <c r="Q24" t="n">
+        <v>1.64</v>
+      </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
@@ -36370,6 +36745,9 @@
       <c r="P25" t="n">
         <v>-0.37</v>
       </c>
+      <c r="Q25" t="n">
+        <v>1.34</v>
+      </c>
       <c r="R25" t="n">
         <v>4.12</v>
       </c>
@@ -36703,6 +37081,9 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.19</v>
+      </c>
       <c r="R26" t="n">
         <v>13.25</v>
       </c>
@@ -37036,6 +37417,9 @@
       <c r="P27" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="Q27" t="n">
+        <v>3.94</v>
+      </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
@@ -37369,6 +37753,9 @@
       <c r="P28" t="n">
         <v>-0.32</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
       <c r="R28" t="n">
         <v>2.08</v>
       </c>
@@ -37702,6 +38089,9 @@
       <c r="P29" t="n">
         <v>-0.18</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1.71</v>
+      </c>
       <c r="R29" t="n">
         <v>2.52</v>
       </c>
@@ -38035,6 +38425,9 @@
       <c r="P30" t="n">
         <v>-0.53</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1.06</v>
+      </c>
       <c r="R30" t="n">
         <v>4.36</v>
       </c>
@@ -38368,6 +38761,9 @@
       <c r="P31" t="n">
         <v>-0.15</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
       <c r="R31" t="n">
         <v>6.04</v>
       </c>
@@ -38695,6 +39091,9 @@
       <c r="P32" t="n">
         <v>-0.04</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="n">
         <v>5.61</v>
       </c>
@@ -39028,6 +39427,9 @@
       <c r="P33" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
       <c r="R33" t="n">
         <v>6.25</v>
       </c>
@@ -39358,6 +39760,9 @@
       <c r="P34" t="n">
         <v>0.22</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.53</v>
+      </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
@@ -39931,6 +40336,9 @@
       </c>
       <c r="N36" t="n">
         <v>1.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>2.9</v>
@@ -40239,7 +40647,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>COEF_OVER1FT</t>
+          <t>COEF_OVER1,5FT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -40476,6 +40884,9 @@
       <c r="P2" t="n">
         <v>0.79</v>
       </c>
+      <c r="Q2" t="n">
+        <v>5.06</v>
+      </c>
       <c r="R2" t="n">
         <v>22</v>
       </c>
@@ -40628,6 +41039,9 @@
       <c r="P3" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="R3" t="n">
         <v>3.89</v>
       </c>
@@ -40783,6 +41197,9 @@
       <c r="P4" t="n">
         <v>-0.12</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="R4" t="n">
         <v>3.04</v>
       </c>
@@ -40932,6 +41349,9 @@
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
@@ -41092,6 +41512,9 @@
       <c r="P6" t="n">
         <v>-0.03</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="R6" t="n">
         <v>3.43</v>
       </c>
@@ -41249,6 +41672,9 @@
       <c r="P7" t="n">
         <v>0.15</v>
       </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
@@ -41406,6 +41832,9 @@
       <c r="P8" t="n">
         <v>0.08</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="R8" t="n">
         <v>1.93</v>
       </c>
@@ -41558,6 +41987,9 @@
       <c r="P9" t="n">
         <v>-0.6</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R9" t="n">
         <v>18.67</v>
       </c>
@@ -41718,6 +42150,9 @@
       <c r="P10" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q10" t="n">
+        <v>2.09</v>
+      </c>
       <c r="R10" t="n">
         <v>3.82</v>
       </c>
@@ -41873,6 +42308,9 @@
       <c r="P11" t="n">
         <v>-0.08</v>
       </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
       <c r="R11" t="n">
         <v>2.56</v>
       </c>
@@ -42033,6 +42471,9 @@
       <c r="P12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
       <c r="R12" t="n">
         <v>2.35</v>
       </c>
@@ -42193,6 +42634,9 @@
       <c r="P13" t="n">
         <v>0.29</v>
       </c>
+      <c r="Q13" t="n">
+        <v>4.17</v>
+      </c>
       <c r="R13" t="n">
         <v>2.39</v>
       </c>
@@ -42300,6 +42744,9 @@
       <c r="P14" t="n">
         <v>-0.16</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
       <c r="R14" t="n">
         <v>2.78</v>
       </c>
@@ -42452,6 +42899,9 @@
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
@@ -42573,6 +43023,9 @@
       <c r="P16" t="n">
         <v>-0.46</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
       <c r="R16" t="n">
         <v>4.96</v>
       </c>
@@ -42733,6 +43186,9 @@
       <c r="P17" t="n">
         <v>-0.31</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
       <c r="R17" t="n">
         <v>3.94</v>
       </c>
@@ -42893,6 +43349,9 @@
       <c r="P18" t="n">
         <v>0.19</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
       <c r="S18" t="n">
         <v>8.56</v>
       </c>
@@ -43003,6 +43462,9 @@
       <c r="N19" t="n">
         <v>1.8</v>
       </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
       <c r="S19" t="n">
         <v>3.04</v>
       </c>
@@ -43116,6 +43578,9 @@
       <c r="P20" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
       <c r="R20" t="n">
         <v>8.25</v>
       </c>
@@ -43270,6 +43735,9 @@
       <c r="P21" t="n">
         <v>-0.45</v>
       </c>
+      <c r="Q21" t="n">
+        <v>1.21</v>
+      </c>
       <c r="R21" t="n">
         <v>3.97</v>
       </c>
@@ -43425,6 +43893,9 @@
       <c r="P22" t="n">
         <v>-0.19</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
       <c r="S22" t="n">
         <v>13.92</v>
       </c>
@@ -43544,6 +44015,9 @@
       <c r="P23" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
       <c r="R23" t="n">
         <v>3.87</v>
       </c>
@@ -43699,6 +44173,9 @@
       <c r="P24" t="n">
         <v>-0.27</v>
       </c>
+      <c r="Q24" t="n">
+        <v>1.64</v>
+      </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
@@ -43854,6 +44331,9 @@
       <c r="P25" t="n">
         <v>-0.37</v>
       </c>
+      <c r="Q25" t="n">
+        <v>1.34</v>
+      </c>
       <c r="R25" t="n">
         <v>4.12</v>
       </c>
@@ -44006,6 +44486,9 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.19</v>
+      </c>
       <c r="R26" t="n">
         <v>13.25</v>
       </c>
@@ -44161,6 +44644,9 @@
       <c r="P27" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="Q27" t="n">
+        <v>3.94</v>
+      </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
@@ -44316,6 +44802,9 @@
       <c r="P28" t="n">
         <v>-0.32</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
       <c r="R28" t="n">
         <v>2.08</v>
       </c>
@@ -44471,6 +44960,9 @@
       <c r="P29" t="n">
         <v>-0.18</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1.71</v>
+      </c>
       <c r="R29" t="n">
         <v>2.52</v>
       </c>
@@ -44631,6 +45123,9 @@
       <c r="P30" t="n">
         <v>-0.53</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1.06</v>
+      </c>
       <c r="R30" t="n">
         <v>4.36</v>
       </c>
@@ -44786,6 +45281,9 @@
       <c r="P31" t="n">
         <v>-0.15</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
       <c r="R31" t="n">
         <v>6.04</v>
       </c>
@@ -44932,6 +45430,9 @@
       <c r="P32" t="n">
         <v>-0.04</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="n">
         <v>5.61</v>
       </c>
@@ -45087,6 +45588,9 @@
       <c r="P33" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
       <c r="R33" t="n">
         <v>6.25</v>
       </c>
@@ -45239,6 +45743,9 @@
       <c r="P34" t="n">
         <v>0.22</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.53</v>
+      </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
@@ -45491,6 +45998,9 @@
       </c>
       <c r="N36" t="n">
         <v>1.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>2.9</v>
@@ -45653,7 +46163,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>COEF_OVER1FT</t>
+          <t>COEF_OVER1,5FT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -47395,6 +47905,9 @@
       <c r="P2" t="n">
         <v>0.79</v>
       </c>
+      <c r="Q2" t="n">
+        <v>5.06</v>
+      </c>
       <c r="R2" t="n">
         <v>22</v>
       </c>
@@ -48464,6 +48977,9 @@
       <c r="P3" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>2.57</v>
+      </c>
       <c r="R3" t="n">
         <v>3.89</v>
       </c>
@@ -49533,6 +50049,9 @@
       <c r="P4" t="n">
         <v>-0.12</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="R4" t="n">
         <v>3.04</v>
       </c>
@@ -50602,6 +51121,9 @@
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
       <c r="R5" t="n">
         <v>3.25</v>
       </c>
@@ -51671,6 +52193,9 @@
       <c r="P6" t="n">
         <v>-0.03</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2.17</v>
+      </c>
       <c r="R6" t="n">
         <v>3.43</v>
       </c>
@@ -52740,6 +53265,9 @@
       <c r="P7" t="n">
         <v>0.15</v>
       </c>
+      <c r="Q7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
@@ -53809,6 +54337,9 @@
       <c r="P8" t="n">
         <v>0.08</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="R8" t="n">
         <v>1.93</v>
       </c>
@@ -54878,6 +55409,9 @@
       <c r="P9" t="n">
         <v>-0.6</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R9" t="n">
         <v>18.67</v>
       </c>
@@ -55952,6 +56486,9 @@
       <c r="P10" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q10" t="n">
+        <v>2.09</v>
+      </c>
       <c r="R10" t="n">
         <v>3.82</v>
       </c>
@@ -57021,6 +57558,9 @@
       <c r="P11" t="n">
         <v>-0.08</v>
       </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
       <c r="R11" t="n">
         <v>2.56</v>
       </c>
@@ -58090,6 +58630,9 @@
       <c r="P12" t="n">
         <v>-0.11</v>
       </c>
+      <c r="Q12" t="n">
+        <v>1.93</v>
+      </c>
       <c r="R12" t="n">
         <v>2.35</v>
       </c>
@@ -59159,6 +59702,9 @@
       <c r="P13" t="n">
         <v>0.29</v>
       </c>
+      <c r="Q13" t="n">
+        <v>4.17</v>
+      </c>
       <c r="R13" t="n">
         <v>2.39</v>
       </c>
@@ -60208,6 +60754,9 @@
       <c r="P14" t="n">
         <v>-0.16</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
       <c r="R14" t="n">
         <v>2.78</v>
       </c>
@@ -61274,6 +61823,9 @@
       <c r="O15" t="n">
         <v>2.06</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
@@ -62313,6 +62865,9 @@
       <c r="P16" t="n">
         <v>-0.46</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1.15</v>
+      </c>
       <c r="R16" t="n">
         <v>4.96</v>
       </c>
@@ -63382,6 +63937,9 @@
       <c r="P17" t="n">
         <v>-0.31</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
       <c r="R17" t="n">
         <v>3.94</v>
       </c>
@@ -64451,6 +65009,9 @@
       <c r="P18" t="n">
         <v>0.19</v>
       </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
       <c r="S18" t="n">
         <v>8.56</v>
       </c>
@@ -65481,6 +66042,9 @@
       <c r="N19" t="n">
         <v>1.8</v>
       </c>
+      <c r="Q19" t="n">
+        <v>2.08</v>
+      </c>
       <c r="S19" t="n">
         <v>3.04</v>
       </c>
@@ -66520,6 +67084,9 @@
       <c r="P20" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q20" t="n">
+        <v>1.59</v>
+      </c>
       <c r="R20" t="n">
         <v>8.25</v>
       </c>
@@ -67589,6 +68156,9 @@
       <c r="P21" t="n">
         <v>-0.45</v>
       </c>
+      <c r="Q21" t="n">
+        <v>1.21</v>
+      </c>
       <c r="R21" t="n">
         <v>3.97</v>
       </c>
@@ -68663,6 +69233,9 @@
       <c r="P22" t="n">
         <v>-0.19</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
       <c r="S22" t="n">
         <v>13.92</v>
       </c>
@@ -69702,6 +70275,9 @@
       <c r="P23" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q23" t="n">
+        <v>1.55</v>
+      </c>
       <c r="R23" t="n">
         <v>3.87</v>
       </c>
@@ -70776,6 +71352,9 @@
       <c r="P24" t="n">
         <v>-0.27</v>
       </c>
+      <c r="Q24" t="n">
+        <v>1.64</v>
+      </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
@@ -71845,6 +72424,9 @@
       <c r="P25" t="n">
         <v>-0.37</v>
       </c>
+      <c r="Q25" t="n">
+        <v>1.34</v>
+      </c>
       <c r="R25" t="n">
         <v>4.12</v>
       </c>
@@ -72914,6 +73496,9 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>2.19</v>
+      </c>
       <c r="R26" t="n">
         <v>13.25</v>
       </c>
@@ -73983,6 +74568,9 @@
       <c r="P27" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="Q27" t="n">
+        <v>3.94</v>
+      </c>
       <c r="R27" t="n">
         <v>1.96</v>
       </c>
@@ -75052,6 +75640,9 @@
       <c r="P28" t="n">
         <v>-0.32</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1.57</v>
+      </c>
       <c r="R28" t="n">
         <v>2.08</v>
       </c>
@@ -76121,6 +76712,9 @@
       <c r="P29" t="n">
         <v>-0.18</v>
       </c>
+      <c r="Q29" t="n">
+        <v>1.71</v>
+      </c>
       <c r="R29" t="n">
         <v>2.52</v>
       </c>
@@ -77190,6 +77784,9 @@
       <c r="P30" t="n">
         <v>-0.53</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1.06</v>
+      </c>
       <c r="R30" t="n">
         <v>4.36</v>
       </c>
@@ -78264,6 +78861,9 @@
       <c r="P31" t="n">
         <v>-0.15</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1.88</v>
+      </c>
       <c r="R31" t="n">
         <v>6.04</v>
       </c>
@@ -79327,6 +79927,9 @@
       <c r="P32" t="n">
         <v>-0.04</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="n">
         <v>5.61</v>
       </c>
@@ -80396,6 +80999,9 @@
       <c r="P33" t="n">
         <v>-0.25</v>
       </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
       <c r="R33" t="n">
         <v>6.25</v>
       </c>
@@ -81283,6 +81889,9 @@
       <c r="P34" t="n">
         <v>0.22</v>
       </c>
+      <c r="Q34" t="n">
+        <v>2.53</v>
+      </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
@@ -83194,6 +83803,9 @@
       </c>
       <c r="N36" t="n">
         <v>1.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
         <v>2.9</v>
